--- a/Archives/Data/3.10.2/base-year_2015/extensions/dom_biogeochemical/F_x_dom.xlsx
+++ b/Archives/Data/3.10.2/base-year_2015/extensions/dom_biogeochemical/F_x_dom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\Archives\Data\3.10.2\base-year_2015\extensions\dom_biogeochemical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBBF495-8DAF-4E54-87FC-6D229B8FFA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CB35FD-ADAC-4AF8-9F0C-B1D9DE4F3B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
